--- a/output/第10期計画_代表KPIの振替案と確認事項の精査.xlsx
+++ b/output/第10期計画_代表KPIの振替案と確認事項の精査.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>「本来であればより適切と思われるサービス」として、区域内に事業所が存在しないサービス（夜間対応型訪問介護・定期巡回・随時対応型訪問介護看護・看護小規模多機能型居宅介護・介護医療院）を1つ以上選んだ票は98票中20票（20.4％）である。「必要と判断されたが区域内で提供できないサービスがある利用者の割合」として定義し直せば、H12の代理指標になる。</t>
+          <t>「本来であればより適切と思われるサービス」として、区域内に事業所が存在しないサービス（夜間対応型訪問介護・定期巡回・随時対応型訪問介護看護・看護小規模多機能型居宅介護・介護医療院）を1つ以上選んだ票は20.2％（99票中20票）である。「必要と判断されたが区域内で提供できないサービスがある利用者の割合」として定義し直せば、H12の代理指標になる。</t>
         </is>
       </c>
     </row>
@@ -1784,17 +1784,17 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>分子：在宅生活改善調査 問3で「本来であればより適切と思われるサービス」として、区域内に事業所が存在しないサービス（夜間対応型訪問介護・定期巡回・随時対応型訪問介護看護・看護小規模多機能型居宅介護・介護医療院）を1つ以上選んだ票／分母：有効票</t>
+          <t>分子：在宅生活改善調査の「本来であればより適切と思われるサービス」として、区域内に事業所が存在しないサービス（夜間対応型訪問介護・定期巡回・随時対応型訪問介護看護・看護小規模多機能型居宅介護・介護医療院）を1つ以上選んだ票／分母：当該設問の有効票</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>20.4％</t>
+          <t>20.2％</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1925,7 +1925,7 @@
       <c r="D15" s="13" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>削除しない。20.4％は代理指標であり、第6章第4節の整備方針を検討する参考情報の一つとして用いる</t>
+          <t>削除しない。20.2％は代理指標であり、第6章第4節の整備方針を検討する参考情報の一つとして用いる</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1955,7 +1955,7 @@
     <row r="18" ht="65" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>注1）4項目とも削除せずに算定できる見込みであり、受託者は4項目とも振替えを案とする。注2）ただしH07・H08・H12は測るものが変わる。計画本文では、第9期の指標との連続性がないことを明記する。注3）H16の算定には、国民健康保険団体連合会の給付実績から業務継続計画未策定減算の算定事業所を抽出していただく必要がある（資料提供依頼に追加する）。注4）H12の基準値20.4％は、区域内に事業所が存在しない4サービスを選んだ票の割合である。内訳（延べ）は看護小規模多機能型居宅介護10票、定期巡回・随時対応型訪問介護看護9票、夜間対応型訪問介護7票、介護医療院3票である。小規模多機能型居宅介護（44票）は区域内に5事業所あるため分子に含めていない。</t>
+          <t>注1）4項目とも削除せずに算定できる見込みであり、受託者は4項目とも振替えを案とする。注2）ただしH07・H08・H12は測るものが変わる。計画本文では、第9期の指標との連続性がないことを明記する。注3）H16の算定には、国民健康保険団体連合会の給付実績から業務継続計画未策定減算の算定事業所を抽出していただく必要がある（資料提供依頼に追加する）。注4）H12の基準値20.2％は、区域内に事業所が存在しない4サービスを選んだ票の割合である。内訳（延べ）は看護小規模多機能型居宅介護10票、定期巡回・随時対応型訪問介護看護9票、夜間対応型訪問介護7票、介護医療院3票である。小規模多機能型居宅介護（44票）は区域内に5事業所あるため分子に含めていない。</t>
         </is>
       </c>
     </row>
